--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T09:28:26+00:00</t>
+    <t>2023-10-16T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/CodeSystem/fr-core-identity-method-collection</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-identity-method-collection</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:15:36+00:00</t>
+    <t>2023-11-07T09:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
+++ b/ig/main/CodeSystem-fr-core-identity-method-collection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
